--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU02/HRM/pre LAM_HRM-2031-0292/Panel 02/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU02/HRM/pre LAM_HRM-2031-0292/Panel 02/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.96028</v>
+        <v>16.72385</v>
       </c>
       <c r="D2" t="n">
-        <v>16.41359</v>
+        <v>16.56137</v>
       </c>
       <c r="E2" t="n">
-        <v>16.44334</v>
+        <v>16.63223</v>
       </c>
       <c r="F2" t="n">
-        <v>42.93485</v>
+        <v>42.68966</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05111</v>
+        <v>0.05002</v>
       </c>
       <c r="H2" t="n">
-        <v>1.8064</v>
+        <v>1.8298</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.52317</v>
+        <v>16.96495</v>
       </c>
       <c r="D3" t="n">
-        <v>16.87699</v>
+        <v>16.30312</v>
       </c>
       <c r="E3" t="n">
-        <v>16.63578</v>
+        <v>16.66632</v>
       </c>
       <c r="F3" t="n">
-        <v>42.38271</v>
+        <v>41.73583</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05011</v>
+        <v>0.05063</v>
       </c>
       <c r="H3" t="n">
-        <v>1.82204</v>
+        <v>1.80726</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.66931</v>
+        <v>16.74257</v>
       </c>
       <c r="D4" t="n">
-        <v>16.81011</v>
+        <v>16.4302</v>
       </c>
       <c r="E4" t="n">
-        <v>16.63602</v>
+        <v>16.64532</v>
       </c>
       <c r="F4" t="n">
-        <v>42.31484</v>
+        <v>42.39667</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05063</v>
+        <v>0.05073</v>
       </c>
       <c r="H4" t="n">
-        <v>1.83651</v>
+        <v>1.80416</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.62038</v>
+        <v>16.68268</v>
       </c>
       <c r="D6" t="n">
-        <v>15.79148</v>
+        <v>15.96536</v>
       </c>
       <c r="E6" t="n">
-        <v>16.2526</v>
+        <v>16.24778</v>
       </c>
       <c r="F6" t="n">
-        <v>22.40009</v>
+        <v>21.72239</v>
       </c>
       <c r="G6" t="n">
-        <v>34.55703</v>
+        <v>33.85408</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.07497</v>
+        <v>16.63371</v>
       </c>
       <c r="D7" t="n">
-        <v>16.18967</v>
+        <v>16.06598</v>
       </c>
       <c r="E7" t="n">
-        <v>16.29741</v>
+        <v>16.38219</v>
       </c>
       <c r="F7" t="n">
-        <v>22.02118</v>
+        <v>21.66985</v>
       </c>
       <c r="G7" t="n">
-        <v>33.48812</v>
+        <v>34.28002</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.89079</v>
+        <v>16.71544</v>
       </c>
       <c r="D8" t="n">
-        <v>15.75698</v>
+        <v>15.66147</v>
       </c>
       <c r="E8" t="n">
-        <v>16.21193</v>
+        <v>16.42227</v>
       </c>
       <c r="F8" t="n">
-        <v>21.58923</v>
+        <v>21.6904</v>
       </c>
       <c r="G8" t="n">
-        <v>33.94063</v>
+        <v>33.34782</v>
       </c>
     </row>
     <row r="9">
@@ -650,10 +650,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.60394</v>
+        <v>0.60131</v>
       </c>
       <c r="D10" t="n">
-        <v>1.1467</v>
+        <v>1.11985</v>
       </c>
     </row>
     <row r="11">
@@ -663,10 +663,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.60843</v>
+        <v>0.61491</v>
       </c>
       <c r="D11" t="n">
-        <v>1.10093</v>
+        <v>1.09895</v>
       </c>
     </row>
     <row r="12">
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.61244</v>
+        <v>0.59598</v>
       </c>
       <c r="D12" t="n">
-        <v>1.12587</v>
+        <v>1.10469</v>
       </c>
     </row>
   </sheetData>
